--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Unity_FinalProject\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5234193-6358-4BCB-8C3D-5B61DDD0B329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28995" yWindow="3240" windowWidth="18630" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="BuildingData" sheetId="1" r:id="rId5"/>
+    <sheet name="BuildingData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>건물 고유 ID</t>
   </si>
@@ -95,22 +104,63 @@
   </si>
   <si>
     <t>Department_Store</t>
+  </si>
+  <si>
+    <t>Building_07_Spawner</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Subway</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 타입
+Normal = 0,
+TownHall = 1,
+Spanwer = 2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -119,43 +169,53 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -345,27 +405,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H1000"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.13"/>
-    <col customWidth="1" min="2" max="2" width="17.5"/>
-    <col customWidth="1" min="3" max="3" width="22.13"/>
-    <col customWidth="1" min="4" max="4" width="34.5"/>
-    <col customWidth="1" min="5" max="5" width="35.5"/>
-    <col customWidth="1" min="6" max="6" width="30.0"/>
-    <col customWidth="1" min="7" max="7" width="36.0"/>
-    <col customWidth="1" min="8" max="26" width="7.88"/>
+    <col min="1" max="1" width="19.125" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="26" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -387,12 +444,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -407,15 +467,18 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -433,8 +496,11 @@
       <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -442,22 +508,25 @@
         <v>17</v>
       </c>
       <c r="C4" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>1.0</v>
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -465,22 +534,25 @@
         <v>19</v>
       </c>
       <c r="C5" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>3.0</v>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -488,22 +560,25 @@
         <v>21</v>
       </c>
       <c r="C6" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>5.0</v>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -511,22 +586,25 @@
         <v>23</v>
       </c>
       <c r="C7" s="1">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>8.0</v>
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -534,22 +612,25 @@
         <v>25</v>
       </c>
       <c r="C8" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>15.0</v>
+        <v>15</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -557,28 +638,56 @@
         <v>27</v>
       </c>
       <c r="C9" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F9" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>40.0</v>
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -1564,9 +1673,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.9843055605888367" footer="0.0" header="0.0" left="0.7480555772781372" right="0.7480555772781372" top="0.9843055605888367"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>건물 고유 ID</t>
   </si>
@@ -34,6 +34,12 @@
     <t>인구 증가량</t>
   </si>
   <si>
+    <t>건물 타입
+Normal = 0,
+TownHall = 1,
+Spanwer = 2</t>
+  </si>
+  <si>
     <t>(name)</t>
   </si>
   <si>
@@ -61,6 +67,9 @@
     <t>CatCapacity</t>
   </si>
   <si>
+    <t>BuildingType</t>
+  </si>
+  <si>
     <t>Building_01_House</t>
   </si>
   <si>
@@ -95,18 +104,40 @@
   </si>
   <si>
     <t>Department_Store</t>
+  </si>
+  <si>
+    <t>Building_07_Spawner</t>
+  </si>
+  <si>
+    <t>Subway</t>
+  </si>
+  <si>
+    <t>Building_08_TownHall</t>
+  </si>
+  <si>
+    <t>TownHall</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
     </font>
     <font>
       <color theme="1"/>
@@ -128,15 +159,24 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -355,14 +395,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.13"/>
-    <col customWidth="1" min="2" max="2" width="17.5"/>
-    <col customWidth="1" min="3" max="3" width="22.13"/>
-    <col customWidth="1" min="4" max="4" width="34.5"/>
-    <col customWidth="1" min="5" max="5" width="35.5"/>
-    <col customWidth="1" min="6" max="6" width="30.0"/>
-    <col customWidth="1" min="7" max="7" width="36.0"/>
-    <col customWidth="1" min="8" max="26" width="7.88"/>
+    <col customWidth="1" min="1" max="1" width="16.75"/>
+    <col customWidth="1" min="2" max="2" width="15.25"/>
+    <col customWidth="1" min="3" max="7" width="13.5"/>
+    <col customWidth="1" min="8" max="8" width="13.88"/>
+    <col customWidth="1" min="9" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -387,39 +424,45 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
+      <c r="H2" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -428,18 +471,21 @@
         <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
@@ -455,14 +501,17 @@
       </c>
       <c r="G4" s="1">
         <v>1.0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1">
         <v>15.0</v>
@@ -478,14 +527,17 @@
       </c>
       <c r="G5" s="1">
         <v>3.0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>20.0</v>
@@ -501,14 +553,17 @@
       </c>
       <c r="G6" s="1">
         <v>5.0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1">
         <v>30.0</v>
@@ -524,14 +579,17 @@
       </c>
       <c r="G7" s="1">
         <v>8.0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>50.0</v>
@@ -547,14 +605,17 @@
       </c>
       <c r="G8" s="1">
         <v>15.0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>100.0</v>
@@ -571,9 +632,62 @@
       <c r="G9" s="1">
         <v>40.0</v>
       </c>
+      <c r="H9" s="4">
+        <v>0.0</v>
+      </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1.0</v>
+      </c>
+    </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
   <si>
     <t>건물 고유 ID</t>
   </si>
@@ -22,13 +22,19 @@
     <t>건물 가격</t>
   </si>
   <si>
+    <t>너비</t>
+  </si>
+  <si>
+    <t>높이</t>
+  </si>
+  <si>
     <t>ScaleX</t>
   </si>
   <si>
     <t>ScaleY</t>
   </si>
   <si>
-    <t>너비</t>
+    <t>땅 오차</t>
   </si>
   <si>
     <t>인구 증가량</t>
@@ -40,6 +46,9 @@
 Spanwer = 2</t>
   </si>
   <si>
+    <t>건물 에셋</t>
+  </si>
+  <si>
     <t>(name)</t>
   </si>
   <si>
@@ -52,6 +61,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>string[]</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -64,58 +76,133 @@
     <t>Width</t>
   </si>
   <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>GroundOffset</t>
+  </si>
+  <si>
     <t>CatCapacity</t>
   </si>
   <si>
     <t>BuildingType</t>
   </si>
   <si>
+    <t>ModelAddresses</t>
+  </si>
+  <si>
     <t>Building_01_House</t>
   </si>
   <si>
     <t>House</t>
   </si>
   <si>
-    <t>Building_02_Shop</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>Building_03_Museum</t>
-  </si>
-  <si>
-    <t>Museum</t>
-  </si>
-  <si>
-    <t>Building_04_Fitness_Center</t>
-  </si>
-  <si>
-    <t>Fitness_Center</t>
-  </si>
-  <si>
-    <t>Building_05_Theater</t>
-  </si>
-  <si>
-    <t>Theater</t>
-  </si>
-  <si>
-    <t>Building_06_Department_Store</t>
-  </si>
-  <si>
-    <t>Department_Store</t>
-  </si>
-  <si>
-    <t>Building_07_Spawner</t>
+    <t>Building_House_Prefab_01,Building_House_Prefab_02,Building_House_Prefab_03,Building_House_Prefab_04</t>
+  </si>
+  <si>
+    <t>Building_02_Cafe</t>
+  </si>
+  <si>
+    <t>Cafe</t>
+  </si>
+  <si>
+    <t>Building_CoffeeShop_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_03_Gym</t>
+  </si>
+  <si>
+    <t>Gym</t>
+  </si>
+  <si>
+    <t>Building_Gym_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_04_Convenience_Store</t>
+  </si>
+  <si>
+    <t>Convenience_Store</t>
+  </si>
+  <si>
+    <t>Building_Convenience_Store_Prefab_01,Building_Convenience_Store_Prefab_02,Building_Convenience_Store_Prefab_03</t>
+  </si>
+  <si>
+    <t>Building_05_Drug_Store</t>
+  </si>
+  <si>
+    <t>Drug_Store</t>
+  </si>
+  <si>
+    <t>Building_Drug_Store_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_05_Hair_Shop</t>
+  </si>
+  <si>
+    <t>Hair_Shop</t>
+  </si>
+  <si>
+    <t>Building_Baber_Shop_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_06_Apartment</t>
+  </si>
+  <si>
+    <t>Apartment</t>
+  </si>
+  <si>
+    <t>Building_Apartment_Prefab_01,Building_Apartment_Prefab_02,Building_Apartment_Prefab_03</t>
+  </si>
+  <si>
+    <t>Building_07_Repair_Shop</t>
+  </si>
+  <si>
+    <t>Repair_Shop</t>
+  </si>
+  <si>
+    <t>Building_Repair_Shop_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_08_Cinema</t>
+  </si>
+  <si>
+    <t>Cinema</t>
+  </si>
+  <si>
+    <t>Building_Cinema_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_09_Mall</t>
+  </si>
+  <si>
+    <t>Mall</t>
+  </si>
+  <si>
+    <t>Building_Mall_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_10_Police_Office</t>
+  </si>
+  <si>
+    <t>Police_Office</t>
+  </si>
+  <si>
+    <t>Building_Police_Office_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_11_Spawner</t>
   </si>
   <si>
     <t>Subway</t>
   </si>
   <si>
-    <t>Building_08_TownHall</t>
+    <t>Building_12_TownHall</t>
   </si>
   <si>
     <t>TownHall</t>
+  </si>
+  <si>
+    <t>Building_TownHall_Prefab_01,Building_TownHall_Prefab_02,Building_TownHall_Prefab_03</t>
   </si>
 </sst>
 </file>
@@ -142,7 +229,6 @@
     <font>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,20 +245,23 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -397,9 +486,8 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="16.75"/>
     <col customWidth="1" min="2" max="2" width="15.25"/>
-    <col customWidth="1" min="3" max="7" width="13.5"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="26" width="11.0"/>
+    <col customWidth="1" min="3" max="9" width="13.5"/>
+    <col customWidth="1" min="10" max="10" width="13.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -427,272 +515,538 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
       </c>
       <c r="D4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.0</v>
       </c>
-      <c r="E4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="J4" s="4">
         <v>0.0</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
-        <v>15.0</v>
+        <v>50.0</v>
       </c>
       <c r="D5" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E5" s="1">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F5" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G5" s="1">
         <v>3.0</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="J5" s="4">
         <v>0.0</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="D6" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="I6" s="1">
         <v>2.0</v>
       </c>
-      <c r="E6" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="J6" s="4">
         <v>0.0</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="D7" s="1">
         <v>3.0</v>
       </c>
       <c r="E7" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F7" s="1">
         <v>3.0</v>
       </c>
       <c r="G7" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="H7" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J7" s="4">
         <v>0.0</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1">
-        <v>50.0</v>
+        <v>1200.0</v>
       </c>
       <c r="D8" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="I8" s="1">
         <v>4.0</v>
       </c>
-      <c r="E8" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="J8" s="4">
         <v>0.0</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1">
-        <v>100.0</v>
+        <v>1500.0</v>
       </c>
       <c r="D9" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="I9" s="1">
         <v>5.0</v>
       </c>
-      <c r="E9" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="J9" s="4">
         <v>0.0</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="4">
+        <v>43</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2000.0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>-2.0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="J10" s="4">
         <v>0.0</v>
       </c>
-      <c r="H10" s="4">
-        <v>2.0</v>
+      <c r="K10" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>32</v>
+      <c r="A11" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="5">
+        <v>47</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2200.0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-1.0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="J11" s="4">
         <v>0.0</v>
       </c>
-      <c r="D11" s="5">
+      <c r="K11" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="I12" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4">
+        <v>6500.0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>25.0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="4">
+        <v>7000.0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>-1.0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="G16" s="4">
         <v>4.0</v>
       </c>
-      <c r="E11" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="H16" s="6">
+        <v>-2.0</v>
+      </c>
+      <c r="I16" s="4">
         <v>0.0</v>
       </c>
-      <c r="H11" s="5">
+      <c r="J16" s="4">
         <v>1.0</v>
       </c>
+      <c r="K16" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>건물 고유 ID</t>
   </si>
@@ -136,7 +136,7 @@
     <t>Building_Drug_Store_Prefab_01</t>
   </si>
   <si>
-    <t>Building_05_Hair_Shop</t>
+    <t>Building_06_Hair_Shop</t>
   </si>
   <si>
     <t>Hair_Shop</t>
@@ -145,7 +145,7 @@
     <t>Building_Baber_Shop_Prefab_01</t>
   </si>
   <si>
-    <t>Building_06_Apartment</t>
+    <t>Building_07_Apartment</t>
   </si>
   <si>
     <t>Apartment</t>
@@ -154,7 +154,7 @@
     <t>Building_Apartment_Prefab_01,Building_Apartment_Prefab_02,Building_Apartment_Prefab_03</t>
   </si>
   <si>
-    <t>Building_07_Repair_Shop</t>
+    <t>Building_08_Repair_Shop</t>
   </si>
   <si>
     <t>Repair_Shop</t>
@@ -163,7 +163,7 @@
     <t>Building_Repair_Shop_Prefab_01</t>
   </si>
   <si>
-    <t>Building_08_Cinema</t>
+    <t>Building_09_Cinema</t>
   </si>
   <si>
     <t>Cinema</t>
@@ -172,7 +172,7 @@
     <t>Building_Cinema_Prefab_01</t>
   </si>
   <si>
-    <t>Building_09_Mall</t>
+    <t>Building_10_Mall</t>
   </si>
   <si>
     <t>Mall</t>
@@ -181,7 +181,7 @@
     <t>Building_Mall_Prefab_01</t>
   </si>
   <si>
-    <t>Building_10_Police_Office</t>
+    <t>Building_11_Police_Office</t>
   </si>
   <si>
     <t>Police_Office</t>
@@ -190,13 +190,16 @@
     <t>Building_Police_Office_Prefab_01</t>
   </si>
   <si>
-    <t>Building_11_Spawner</t>
+    <t>Building_12_Spawner</t>
   </si>
   <si>
     <t>Subway</t>
   </si>
   <si>
-    <t>Building_12_TownHall</t>
+    <t>Building_Spawner_Prefab_01</t>
+  </si>
+  <si>
+    <t>Building_13_TownHall</t>
   </si>
   <si>
     <t>TownHall</t>
@@ -209,7 +212,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -230,6 +233,11 @@
       <color theme="1"/>
       <name val="Malgun Gothic"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -245,15 +253,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -264,7 +269,13 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
@@ -512,16 +523,16 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -547,16 +558,16 @@
       <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -582,16 +593,16 @@
       <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -617,16 +628,16 @@
       <c r="G4" s="1">
         <v>2.0</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>-1.0</v>
       </c>
       <c r="I4" s="1">
         <v>1.0</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>0.0</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -652,16 +663,16 @@
       <c r="G5" s="1">
         <v>3.0</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>-1.5</v>
       </c>
       <c r="I5" s="1">
         <v>2.0</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>0.0</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -687,16 +698,16 @@
       <c r="G6" s="1">
         <v>3.0</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>-1.5</v>
       </c>
       <c r="I6" s="1">
         <v>2.0</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>0.0</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -722,16 +733,16 @@
       <c r="G7" s="1">
         <v>2.0</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>-1.0</v>
       </c>
       <c r="I7" s="1">
         <v>3.0</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>0.0</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -757,21 +768,21 @@
       <c r="G8" s="1">
         <v>1.0</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>-0.5</v>
       </c>
       <c r="I8" s="1">
         <v>4.0</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>0.0</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -792,21 +803,21 @@
       <c r="G9" s="1">
         <v>3.0</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>-1.5</v>
       </c>
       <c r="I9" s="1">
         <v>5.0</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>0.0</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -827,224 +838,227 @@
       <c r="G10" s="1">
         <v>4.0</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>-2.0</v>
       </c>
       <c r="I10" s="1">
         <v>8.0</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>0.0</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>2200.0</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>6.0</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>3.0</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>6.0</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>2.0</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="3">
         <v>-1.0</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="3">
         <v>10.0</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="3">
         <v>0.0</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>5000.0</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>10.0</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>5.0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>10.0</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>3.0</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="3">
         <v>-1.5</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="3">
         <v>20.0</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="3">
         <v>0.0</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>6500.0</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>12.0</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>3.0</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="3">
         <v>11.0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>1.0</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="3">
         <v>0.0</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="3">
         <v>25.0</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="3">
         <v>0.0</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>7000.0</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>7.0</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="3">
         <v>3.0</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="3">
         <v>7.0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>2.0</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="3">
         <v>-1.0</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="3">
         <v>10.0</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="3">
         <v>0.0</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>10.0</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F15" s="3">
         <v>1.0</v>
       </c>
-      <c r="E15" s="4">
+      <c r="G15" s="3">
         <v>1.0</v>
       </c>
-      <c r="F15" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>1.0</v>
-      </c>
       <c r="H15" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="I15" s="3">
         <v>0.0</v>
       </c>
-      <c r="I15" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="4">
+      <c r="J15" s="3">
         <v>2.0</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="4">
+      <c r="B16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="3">
         <v>0.0</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>6.0</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>6.0</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="3">
         <v>6.0</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G16" s="3">
         <v>4.0</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="3">
         <v>-2.0</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="3">
         <v>0.0</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="3">
         <v>1.0</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>62</v>
+      <c r="K16" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -707,6 +707,9 @@
       <c r="K4" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="M4" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -742,6 +745,9 @@
       <c r="K5" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="M5" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -818,6 +824,9 @@
       <c r="K7" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="M7" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -894,6 +903,9 @@
       <c r="K9" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="M9" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -970,6 +982,9 @@
       <c r="K11" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="M11" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
@@ -1005,6 +1020,9 @@
       <c r="K12" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="M12" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
@@ -1122,6 +1140,9 @@
       <c r="K15" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="M15" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
@@ -1156,6 +1177,9 @@
       </c>
       <c r="K16" s="1" t="s">
         <v>72</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -136,7 +136,7 @@
     <t>Building_01_House</t>
   </si>
   <si>
-    <t>House</t>
+    <t>주택</t>
   </si>
   <si>
     <t>Building_House_Prefab_01,Building_House_Prefab_02,Building_House_Prefab_03,Building_House_Prefab_04</t>
@@ -145,7 +145,7 @@
     <t>Building_02_Cafe</t>
   </si>
   <si>
-    <t>Cafe</t>
+    <t>카페</t>
   </si>
   <si>
     <t>Building_CoffeeShop_Prefab_01</t>
@@ -154,7 +154,7 @@
     <t>Building_03_Gym</t>
   </si>
   <si>
-    <t>Gym</t>
+    <t>헬스장</t>
   </si>
   <si>
     <t>Building_Gym_Prefab_01</t>
@@ -166,7 +166,7 @@
     <t>Building_04_Convenience_Store</t>
   </si>
   <si>
-    <t>Convenience_Store</t>
+    <t>편의점</t>
   </si>
   <si>
     <t>Building_Convenience_Store_Prefab_01,Building_Convenience_Store_Prefab_02,Building_Convenience_Store_Prefab_03</t>
@@ -175,7 +175,7 @@
     <t>Building_05_Drug_Store</t>
   </si>
   <si>
-    <t>Drug_Store</t>
+    <t>약국</t>
   </si>
   <si>
     <t>Building_Drug_Store_Prefab_01</t>
@@ -187,7 +187,7 @@
     <t>Building_06_Hair_Shop</t>
   </si>
   <si>
-    <t>Hair_Shop</t>
+    <t>헤어샵</t>
   </si>
   <si>
     <t>Building_Baber_Shop_Prefab_01</t>
@@ -196,7 +196,7 @@
     <t>Building_07_Apartment</t>
   </si>
   <si>
-    <t>Apartment</t>
+    <t>아파트</t>
   </si>
   <si>
     <t>Building_Apartment_Prefab_01,Building_Apartment_Prefab_02,Building_Apartment_Prefab_03</t>
@@ -208,7 +208,7 @@
     <t>Building_08_Repair_Shop</t>
   </si>
   <si>
-    <t>Repair_Shop</t>
+    <t>정비소</t>
   </si>
   <si>
     <t>Building_Repair_Shop_Prefab_01</t>
@@ -217,7 +217,7 @@
     <t>Building_09_Cinema</t>
   </si>
   <si>
-    <t>Cinema</t>
+    <t>영화관</t>
   </si>
   <si>
     <t>Building_Cinema_Prefab_01</t>
@@ -226,7 +226,7 @@
     <t>Building_10_Mall</t>
   </si>
   <si>
-    <t>Mall</t>
+    <t>대형 마트</t>
   </si>
   <si>
     <t>Building_Mall_Prefab_01</t>
@@ -238,7 +238,7 @@
     <t>Building_11_Police_Office</t>
   </si>
   <si>
-    <t>Police_Office</t>
+    <t>경찰서</t>
   </si>
   <si>
     <t>Building_Police_Office_Prefab_01</t>
@@ -250,7 +250,7 @@
     <t>Building_12_Spawner</t>
   </si>
   <si>
-    <t>Subway</t>
+    <t>지하철 역</t>
   </si>
   <si>
     <t>Building_Spawner_Prefab_01</t>
@@ -259,7 +259,7 @@
     <t>Building_13_TownHall</t>
   </si>
   <si>
-    <t>TownHall</t>
+    <t>시청</t>
   </si>
   <si>
     <t>Building_TownHall_Prefab_01,Building_TownHall_Prefab_02,Building_TownHall_Prefab_03</t>
@@ -289,7 +289,6 @@
     <font>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -306,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -316,13 +315,14 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -547,7 +547,7 @@
     <col customWidth="1" min="3" max="9" width="13.63"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
     <col customWidth="1" min="11" max="11" width="89.38"/>
-    <col customWidth="1" min="12" max="26" width="12.75"/>
+    <col customWidth="1" min="12" max="13" width="12.75"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -677,7 +677,7 @@
       <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="1">
@@ -686,13 +686,13 @@
       <c r="D4" s="1">
         <v>10.5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="1">
         <v>14.0</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="1">
         <v>10.0</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="1">
         <v>14.0</v>
       </c>
       <c r="H4" s="1">
@@ -715,7 +715,7 @@
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="1">
@@ -724,13 +724,13 @@
       <c r="D5" s="1">
         <v>10.5</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="1">
         <v>16.0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="1">
         <v>10.0</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="1">
         <v>16.0</v>
       </c>
       <c r="H5" s="1">
@@ -753,7 +753,7 @@
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="1">
@@ -762,13 +762,13 @@
       <c r="D6" s="1">
         <v>10.5</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="1">
         <v>12.0</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="1">
         <v>10.0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="1">
         <v>12.0</v>
       </c>
       <c r="H6" s="1">
@@ -794,7 +794,7 @@
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="1">
@@ -803,13 +803,13 @@
       <c r="D7" s="1">
         <v>10.8</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="1">
         <v>11.0</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="1">
         <v>10.0</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="1">
         <v>11.0</v>
       </c>
       <c r="H7" s="1">
@@ -832,7 +832,7 @@
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="1">
@@ -841,13 +841,13 @@
       <c r="D8" s="1">
         <v>11.0</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="1">
         <v>7.0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="1">
         <v>11.0</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="1">
         <v>7.0</v>
       </c>
       <c r="H8" s="1">
@@ -873,7 +873,7 @@
       <c r="A9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="1">
@@ -882,13 +882,13 @@
       <c r="D9" s="1">
         <v>10.4</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="1">
         <v>12.0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="1">
         <v>10.0</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="1">
         <v>12.0</v>
       </c>
       <c r="H9" s="1">
@@ -911,7 +911,7 @@
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="1">
@@ -920,13 +920,13 @@
       <c r="D10" s="1">
         <v>11.5</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="1">
         <v>17.0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="1">
         <v>11.0</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="1">
         <v>17.0</v>
       </c>
       <c r="H10" s="1">
@@ -952,7 +952,7 @@
       <c r="A11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C11" s="1">
@@ -961,13 +961,13 @@
       <c r="D11" s="1">
         <v>21.5</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="1">
         <v>10.0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="1">
         <v>21.0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="1">
         <v>10.0</v>
       </c>
       <c r="H11" s="1">
@@ -990,7 +990,7 @@
       <c r="A12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="1">
@@ -999,13 +999,13 @@
       <c r="D12" s="1">
         <v>31.5</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="1">
         <v>15.0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="1">
         <v>31.0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="1">
         <v>15.0</v>
       </c>
       <c r="H12" s="1">
@@ -1028,25 +1028,25 @@
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>60</v>
       </c>
       <c r="C13" s="1">
         <v>6500.0</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="1">
         <v>38.5</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="1">
         <v>8.0</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="1">
         <v>38.0</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="1">
         <v>8.0</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="1">
         <v>-0.5</v>
       </c>
       <c r="I13" s="1">
@@ -1069,7 +1069,7 @@
       <c r="A14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="1">
@@ -1078,13 +1078,13 @@
       <c r="D14" s="1">
         <v>24.5</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="1">
         <v>10.0</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="1">
         <v>24.0</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="1">
         <v>10.0</v>
       </c>
       <c r="H14" s="1">
@@ -1110,7 +1110,7 @@
       <c r="A15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C15" s="1">
@@ -1119,13 +1119,13 @@
       <c r="D15" s="1">
         <v>5.2</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="1">
         <v>6.0</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="1">
         <v>5.0</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="1">
         <v>6.0</v>
       </c>
       <c r="H15" s="1">
@@ -1148,7 +1148,7 @@
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="1">
@@ -1157,13 +1157,13 @@
       <c r="D16" s="1">
         <v>20.5</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="1">
         <v>20.0</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="1">
         <v>20.0</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="1">
         <v>20.0</v>
       </c>
       <c r="H16" s="1">

--- a/JsonConverter/ExcelFiles/BuildingData.xlsx
+++ b/JsonConverter/ExcelFiles/BuildingData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <r>
       <rPr>
@@ -41,12 +41,6 @@
   </si>
   <si>
     <t>높이</t>
-  </si>
-  <si>
-    <t>ScaleX</t>
-  </si>
-  <si>
-    <t>ScaleY</t>
   </si>
   <si>
     <t>땅 오차</t>
@@ -264,12 +258,21 @@
   <si>
     <t>Building_TownHall_Prefab_01,Building_TownHall_Prefab_02,Building_TownHall_Prefab_03</t>
   </si>
+  <si>
+    <t>Building_14_TownHall</t>
+  </si>
+  <si>
+    <t>랜드마크</t>
+  </si>
+  <si>
+    <t>Building_EndingStatu_Prefab_01</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -290,6 +293,11 @@
       <color theme="1"/>
       <name val="Malgun Gothic"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -305,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -319,11 +327,8 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,10 +549,10 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="16.88"/>
     <col customWidth="1" min="2" max="2" width="15.38"/>
-    <col customWidth="1" min="3" max="9" width="13.63"/>
-    <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="11" width="89.38"/>
-    <col customWidth="1" min="12" max="13" width="12.75"/>
+    <col customWidth="1" min="3" max="7" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="14.0"/>
+    <col customWidth="1" min="9" max="9" width="89.38"/>
+    <col customWidth="1" min="10" max="11" width="12.75"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -572,113 +577,95 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>15</v>
+      <c r="J2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
@@ -690,33 +677,27 @@
         <v>14.0</v>
       </c>
       <c r="F4" s="1">
-        <v>10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G4" s="1">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="H4" s="1">
-        <v>-1.0</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C5" s="1">
         <v>50.0</v>
@@ -728,33 +709,27 @@
         <v>16.0</v>
       </c>
       <c r="F5" s="1">
-        <v>10.0</v>
+        <v>-1.5</v>
       </c>
       <c r="G5" s="1">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="H5" s="1">
-        <v>-1.5</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>60.0</v>
@@ -766,36 +741,30 @@
         <v>12.0</v>
       </c>
       <c r="F6" s="1">
-        <v>10.0</v>
+        <v>-1.5</v>
       </c>
       <c r="G6" s="1">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="H6" s="1">
-        <v>-1.5</v>
-      </c>
-      <c r="I6" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="3">
         <v>5.0</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C7" s="1">
         <v>50.0</v>
@@ -807,33 +776,27 @@
         <v>11.0</v>
       </c>
       <c r="F7" s="1">
-        <v>10.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G7" s="1">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="H7" s="1">
-        <v>-1.0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C8" s="1">
         <v>1200.0</v>
@@ -845,36 +808,30 @@
         <v>7.0</v>
       </c>
       <c r="F8" s="1">
-        <v>11.0</v>
+        <v>-0.5</v>
       </c>
       <c r="G8" s="1">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H8" s="1">
-        <v>-0.5</v>
-      </c>
-      <c r="I8" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="3">
         <v>5.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C9" s="1">
         <v>1500.0</v>
@@ -886,33 +843,27 @@
         <v>12.0</v>
       </c>
       <c r="F9" s="1">
-        <v>10.0</v>
+        <v>-1.5</v>
       </c>
       <c r="G9" s="1">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.5</v>
-      </c>
-      <c r="I9" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C10" s="1">
         <v>2000.0</v>
@@ -924,36 +875,30 @@
         <v>17.0</v>
       </c>
       <c r="F10" s="1">
-        <v>11.0</v>
+        <v>-2.0</v>
       </c>
       <c r="G10" s="1">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="1">
-        <v>-2.0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="3">
         <v>5.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C11" s="1">
         <v>2200.0</v>
@@ -965,33 +910,27 @@
         <v>10.0</v>
       </c>
       <c r="F11" s="1">
-        <v>21.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G11" s="1">
         <v>10.0</v>
       </c>
       <c r="H11" s="1">
-        <v>-1.0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="C12" s="1">
         <v>5000.0</v>
@@ -1003,33 +942,27 @@
         <v>15.0</v>
       </c>
       <c r="F12" s="1">
-        <v>31.0</v>
+        <v>-1.5</v>
       </c>
       <c r="G12" s="1">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="H12" s="1">
-        <v>-1.5</v>
-      </c>
-      <c r="I12" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C13" s="1">
         <v>6500.0</v>
@@ -1041,36 +974,30 @@
         <v>8.0</v>
       </c>
       <c r="F13" s="1">
-        <v>38.0</v>
+        <v>-0.5</v>
       </c>
       <c r="G13" s="1">
-        <v>8.0</v>
+        <v>25.0</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.5</v>
-      </c>
-      <c r="I13" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K13" s="3">
         <v>10.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="C14" s="1">
         <v>7000.0</v>
@@ -1082,36 +1009,30 @@
         <v>10.0</v>
       </c>
       <c r="F14" s="1">
-        <v>24.0</v>
+        <v>-1.0</v>
       </c>
       <c r="G14" s="1">
         <v>10.0</v>
       </c>
       <c r="H14" s="1">
-        <v>-1.0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="3">
         <v>10.0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C15" s="1">
         <v>10.0</v>
@@ -1123,33 +1044,27 @@
         <v>6.0</v>
       </c>
       <c r="F15" s="1">
-        <v>5.0</v>
+        <v>-0.5</v>
       </c>
       <c r="G15" s="1">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.5</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="1">
         <v>2.0</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="I15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C16" s="1">
         <v>0.0</v>
@@ -1161,28 +1076,53 @@
         <v>20.0</v>
       </c>
       <c r="F16" s="1">
-        <v>20.0</v>
+        <v>-2.0</v>
       </c>
       <c r="G16" s="1">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="H16" s="1">
-        <v>-2.0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="1">
         <v>1.0</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="I16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="3">
+      <c r="C17" s="5">
+        <v>99999.0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>19.0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>27.0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" s="5">
         <v>0.0</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
